--- a/MeasureControl/液压测试脚本V2.xlsx
+++ b/MeasureControl/液压测试脚本V2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\20260424\MeasureControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\jiaoben\MeasureControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F161AB4C-973E-4A35-A2BD-34D6F44EFEBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D437167E-41F5-46BB-9358-08F2B3965CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -161,10 +161,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>判据</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -714,6 +710,10 @@
   </si>
   <si>
     <t>mV</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>判据参数</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -919,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -969,7 +969,22 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -979,24 +994,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1301,24 +1298,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>34</v>
@@ -1333,19 +1330,19 @@
         <v>38</v>
       </c>
       <c r="F2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>73</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>74</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>41</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>43</v>
+        <v>189</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>42</v>
@@ -1355,740 +1352,740 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="22" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K3" s="9"/>
       <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="21"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>75</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>76</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K4" s="9"/>
       <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>45</v>
+      <c r="A5" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>47</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>48</v>
       </c>
       <c r="K5" s="10"/>
       <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>82</v>
-      </c>
       <c r="I6" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" s="17" t="s">
+      <c r="A7" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="17" t="s">
+      <c r="F7" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>40</v>
-      </c>
       <c r="G7" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K7" s="10"/>
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
       <c r="E8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="17"/>
+        <v>84</v>
+      </c>
+      <c r="F8" s="20"/>
       <c r="G8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="I8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
       <c r="E9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="16"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>51</v>
+      <c r="A10" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H10" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>99</v>
       </c>
       <c r="K10" s="9"/>
       <c r="L10" s="16"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H11" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="J11" s="13" t="s">
         <v>98</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>99</v>
       </c>
       <c r="K11" s="9"/>
       <c r="L11" s="16"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>54</v>
+      <c r="C12" s="20" t="s">
+        <v>53</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H12" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="J12" s="13" t="s">
         <v>105</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="K12" s="9"/>
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="I13" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>105</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="K13" s="9"/>
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H14" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I14" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="J14" s="13" t="s">
         <v>105</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>106</v>
       </c>
       <c r="K14" s="9"/>
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>55</v>
+      <c r="A15" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H15" s="8" t="s">
+      <c r="I15" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16" s="8" t="s">
+      <c r="I16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J16" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="K16" s="9"/>
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J17" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H18" s="8" t="s">
+      <c r="I18" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J18" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="K18" s="9"/>
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F19" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J19" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="K19" s="9"/>
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F20" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="G20" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H20" s="8" t="s">
+      <c r="I20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J20" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>131</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>56</v>
+      <c r="A21" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="I21" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="I21" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="26" t="s">
-        <v>188</v>
+      <c r="J21" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="K21" s="9"/>
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
+      <c r="A22" s="18"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="I22" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J22" s="26" t="s">
-        <v>188</v>
+      <c r="J22" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="K22" s="9"/>
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I23" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K23" s="9"/>
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>40</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>40</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K24" s="9"/>
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I25" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="I25" s="13" t="s">
+      <c r="J25" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>146</v>
       </c>
       <c r="K25" s="9"/>
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="25"/>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
       <c r="D26" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="G26" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="I26" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="I26" s="13" t="s">
+      <c r="J26" s="13" t="s">
         <v>145</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>146</v>
       </c>
       <c r="K26" s="9"/>
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="17" t="s">
-        <v>57</v>
+      <c r="C27" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>3</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J27" s="8" t="s">
         <v>4</v>
@@ -2097,26 +2094,26 @@
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="20"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>4</v>
@@ -2125,26 +2122,26 @@
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
       <c r="D29" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>4</v>
@@ -2153,26 +2150,26 @@
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>4</v>
@@ -2181,26 +2178,26 @@
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J31" s="8" t="s">
         <v>4</v>
@@ -2209,26 +2206,26 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
+      <c r="A32" s="20"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
       <c r="D32" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E32" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J32" s="8" t="s">
         <v>4</v>
@@ -2237,26 +2234,26 @@
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="A33" s="20"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
       <c r="D33" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>4</v>
@@ -2265,26 +2262,26 @@
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
       <c r="D34" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E34" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J34" s="8" t="s">
         <v>4</v>
@@ -2293,26 +2290,26 @@
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
       <c r="D35" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>4</v>
@@ -2321,26 +2318,26 @@
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
       <c r="D36" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E36" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>4</v>
@@ -2349,26 +2346,26 @@
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
       <c r="D37" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>4</v>
@@ -2377,26 +2374,26 @@
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
       <c r="D38" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E38" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>4</v>
@@ -2405,26 +2402,26 @@
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
       <c r="D39" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E39" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F39" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>4</v>
@@ -2433,26 +2430,26 @@
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E40" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F40" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>4</v>
@@ -2461,26 +2458,26 @@
       <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="A41" s="20"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>4</v>
@@ -2489,26 +2486,26 @@
       <c r="L41" s="14"/>
     </row>
     <row r="42" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="A42" s="20"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
       <c r="D42" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E42" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F42" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>20</v>
@@ -2517,26 +2514,26 @@
       <c r="L42" s="14"/>
     </row>
     <row r="43" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
       <c r="D43" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F43" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J43" s="8" t="s">
         <v>20</v>
@@ -2545,26 +2542,26 @@
       <c r="L43" s="14"/>
     </row>
     <row r="44" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
       <c r="D44" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J44" s="8" t="s">
         <v>4</v>
@@ -2573,26 +2570,26 @@
       <c r="L44" s="14"/>
     </row>
     <row r="45" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
+      <c r="A45" s="20"/>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
       <c r="D45" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>4</v>
@@ -2601,26 +2598,26 @@
       <c r="L45" s="14"/>
     </row>
     <row r="46" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="A46" s="20"/>
+      <c r="B46" s="20"/>
+      <c r="C46" s="20"/>
       <c r="D46" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F46" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J46" s="8" t="s">
         <v>4</v>
@@ -2629,26 +2626,26 @@
       <c r="L46" s="14"/>
     </row>
     <row r="47" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="17"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="20"/>
       <c r="D47" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F47" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J47" s="8" t="s">
         <v>4</v>
@@ -2657,26 +2654,26 @@
       <c r="L47" s="14"/>
     </row>
     <row r="48" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="17"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
       <c r="D48" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F48" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J48" s="8" t="s">
         <v>4</v>
@@ -2685,26 +2682,26 @@
       <c r="L48" s="14"/>
     </row>
     <row r="49" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
+      <c r="A49" s="20"/>
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
       <c r="D49" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F49" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>4</v>
@@ -2713,26 +2710,26 @@
       <c r="L49" s="14"/>
     </row>
     <row r="50" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
+      <c r="A50" s="20"/>
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
       <c r="D50" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F50" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>4</v>
@@ -2741,26 +2738,26 @@
       <c r="L50" s="14"/>
     </row>
     <row r="51" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="17"/>
+      <c r="A51" s="20"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
       <c r="D51" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E51" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J51" s="8" t="s">
         <v>4</v>
@@ -2769,26 +2766,26 @@
       <c r="L51" s="14"/>
     </row>
     <row r="52" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
+      <c r="A52" s="20"/>
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F52" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J52" s="8" t="s">
         <v>4</v>
@@ -2797,26 +2794,26 @@
       <c r="L52" s="14"/>
     </row>
     <row r="53" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="A53" s="20"/>
+      <c r="B53" s="20"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F53" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J53" s="8" t="s">
         <v>4</v>
@@ -2825,28 +2822,28 @@
       <c r="L53" s="14"/>
     </row>
     <row r="54" spans="1:12" s="3" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17" t="s">
-        <v>58</v>
+      <c r="A54" s="20"/>
+      <c r="B54" s="20"/>
+      <c r="C54" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>3</v>
       </c>
       <c r="F54" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J54" s="8" t="s">
         <v>20</v>
@@ -2855,26 +2852,26 @@
       <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
+      <c r="A55" s="20"/>
+      <c r="B55" s="20"/>
+      <c r="C55" s="20"/>
       <c r="D55" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F55" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J55" s="8" t="s">
         <v>20</v>
@@ -2883,26 +2880,26 @@
       <c r="L55" s="14"/>
     </row>
     <row r="56" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="17"/>
+      <c r="A56" s="20"/>
+      <c r="B56" s="20"/>
+      <c r="C56" s="20"/>
       <c r="D56" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>6</v>
       </c>
       <c r="F56" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>20</v>
@@ -2911,26 +2908,26 @@
       <c r="L56" s="14"/>
     </row>
     <row r="57" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="A57" s="20"/>
+      <c r="B57" s="20"/>
+      <c r="C57" s="20"/>
       <c r="D57" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>7</v>
       </c>
       <c r="F57" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>20</v>
@@ -2939,26 +2936,26 @@
       <c r="L57" s="14"/>
     </row>
     <row r="58" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
+      <c r="A58" s="20"/>
+      <c r="B58" s="20"/>
+      <c r="C58" s="20"/>
       <c r="D58" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J58" s="8" t="s">
         <v>20</v>
@@ -2967,26 +2964,26 @@
       <c r="L58" s="14"/>
     </row>
     <row r="59" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
+      <c r="A59" s="20"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
       <c r="D59" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F59" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>20</v>
@@ -2995,26 +2992,26 @@
       <c r="L59" s="14"/>
     </row>
     <row r="60" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
+      <c r="A60" s="20"/>
+      <c r="B60" s="20"/>
+      <c r="C60" s="20"/>
       <c r="D60" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E60" s="8" t="s">
         <v>10</v>
       </c>
       <c r="F60" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J60" s="8" t="s">
         <v>20</v>
@@ -3023,26 +3020,26 @@
       <c r="L60" s="14"/>
     </row>
     <row r="61" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
+      <c r="A61" s="20"/>
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
       <c r="D61" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E61" s="8" t="s">
         <v>11</v>
       </c>
       <c r="F61" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>20</v>
@@ -3051,26 +3048,26 @@
       <c r="L61" s="14"/>
     </row>
     <row r="62" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
+      <c r="A62" s="20"/>
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
       <c r="D62" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>12</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J62" s="8" t="s">
         <v>20</v>
@@ -3079,26 +3076,26 @@
       <c r="L62" s="14"/>
     </row>
     <row r="63" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="17"/>
+      <c r="A63" s="20"/>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
       <c r="D63" s="8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J63" s="8" t="s">
         <v>20</v>
@@ -3107,26 +3104,26 @@
       <c r="L63" s="14"/>
     </row>
     <row r="64" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="17"/>
+      <c r="A64" s="20"/>
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
       <c r="D64" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E64" s="8" t="s">
         <v>14</v>
       </c>
       <c r="F64" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J64" s="8" t="s">
         <v>20</v>
@@ -3135,26 +3132,26 @@
       <c r="L64" s="14"/>
     </row>
     <row r="65" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="17"/>
+      <c r="A65" s="20"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
       <c r="D65" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J65" s="8" t="s">
         <v>20</v>
@@ -3163,26 +3160,26 @@
       <c r="L65" s="14"/>
     </row>
     <row r="66" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="17"/>
+      <c r="A66" s="20"/>
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
       <c r="D66" s="8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E66" s="8" t="s">
         <v>16</v>
       </c>
       <c r="F66" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J66" s="8" t="s">
         <v>20</v>
@@ -3191,26 +3188,26 @@
       <c r="L66" s="14"/>
     </row>
     <row r="67" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="17"/>
+      <c r="A67" s="20"/>
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
       <c r="D67" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E67" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F67" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J67" s="8" t="s">
         <v>20</v>
@@ -3219,26 +3216,26 @@
       <c r="L67" s="14"/>
     </row>
     <row r="68" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="17"/>
+      <c r="A68" s="20"/>
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
       <c r="D68" s="8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E68" s="8" t="s">
         <v>18</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J68" s="8" t="s">
         <v>20</v>
@@ -3247,26 +3244,26 @@
       <c r="L68" s="14"/>
     </row>
     <row r="69" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
+      <c r="A69" s="20"/>
+      <c r="B69" s="20"/>
+      <c r="C69" s="20"/>
       <c r="D69" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E69" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F69" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J69" s="8" t="s">
         <v>4</v>
@@ -3275,26 +3272,26 @@
       <c r="L69" s="14"/>
     </row>
     <row r="70" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="17"/>
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
+      <c r="A70" s="20"/>
+      <c r="B70" s="20"/>
+      <c r="C70" s="20"/>
       <c r="D70" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E70" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F70" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J70" s="8" t="s">
         <v>4</v>
@@ -3303,26 +3300,26 @@
       <c r="L70" s="14"/>
     </row>
     <row r="71" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
+      <c r="A71" s="20"/>
+      <c r="B71" s="20"/>
+      <c r="C71" s="20"/>
       <c r="D71" s="8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F71" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J71" s="8" t="s">
         <v>20</v>
@@ -3331,26 +3328,26 @@
       <c r="L71" s="14"/>
     </row>
     <row r="72" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="17"/>
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
+      <c r="A72" s="20"/>
+      <c r="B72" s="20"/>
+      <c r="C72" s="20"/>
       <c r="D72" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E72" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F72" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J72" s="8" t="s">
         <v>20</v>
@@ -3359,26 +3356,26 @@
       <c r="L72" s="14"/>
     </row>
     <row r="73" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="17"/>
-      <c r="B73" s="17"/>
-      <c r="C73" s="17"/>
+      <c r="A73" s="20"/>
+      <c r="B73" s="20"/>
+      <c r="C73" s="20"/>
       <c r="D73" s="8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E73" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J73" s="8" t="s">
         <v>20</v>
@@ -3387,26 +3384,26 @@
       <c r="L73" s="14"/>
     </row>
     <row r="74" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="17"/>
-      <c r="B74" s="17"/>
-      <c r="C74" s="17"/>
+      <c r="A74" s="20"/>
+      <c r="B74" s="20"/>
+      <c r="C74" s="20"/>
       <c r="D74" s="8" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E74" s="8" t="s">
         <v>25</v>
       </c>
       <c r="F74" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J74" s="8" t="s">
         <v>20</v>
@@ -3415,26 +3412,26 @@
       <c r="L74" s="14"/>
     </row>
     <row r="75" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="17"/>
-      <c r="B75" s="17"/>
-      <c r="C75" s="17"/>
+      <c r="A75" s="20"/>
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
       <c r="D75" s="8" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F75" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>20</v>
@@ -3443,26 +3440,26 @@
       <c r="L75" s="14"/>
     </row>
     <row r="76" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="17"/>
-      <c r="B76" s="17"/>
-      <c r="C76" s="17"/>
+      <c r="A76" s="20"/>
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
       <c r="D76" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E76" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F76" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J76" s="8" t="s">
         <v>20</v>
@@ -3471,26 +3468,26 @@
       <c r="L76" s="14"/>
     </row>
     <row r="77" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="17"/>
-      <c r="B77" s="17"/>
-      <c r="C77" s="17"/>
+      <c r="A77" s="20"/>
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
       <c r="D77" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F77" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>20</v>
@@ -3499,26 +3496,26 @@
       <c r="L77" s="14"/>
     </row>
     <row r="78" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="17"/>
-      <c r="B78" s="17"/>
-      <c r="C78" s="17"/>
+      <c r="A78" s="20"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
       <c r="D78" s="8" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J78" s="8" t="s">
         <v>20</v>
@@ -3527,26 +3524,26 @@
       <c r="L78" s="14"/>
     </row>
     <row r="79" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="17"/>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
+      <c r="A79" s="20"/>
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
       <c r="D79" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E79" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>4</v>
@@ -3555,26 +3552,26 @@
       <c r="L79" s="14"/>
     </row>
     <row r="80" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
+      <c r="A80" s="20"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
       <c r="D80" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E80" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F80" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J80" s="8" t="s">
         <v>4</v>
@@ -3583,379 +3580,379 @@
       <c r="L80" s="14"/>
     </row>
     <row r="81" spans="1:12" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="B81" s="17" t="s">
+      <c r="A81" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B81" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="D81" s="17" t="s">
+      <c r="C81" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="D81" s="20" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F81" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F81" s="20" t="s">
         <v>40</v>
       </c>
       <c r="G81" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H81" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H81" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I81" s="17" t="s">
+      <c r="I81" s="20" t="s">
         <v>40</v>
       </c>
       <c r="J81" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K81" s="9"/>
       <c r="L81" s="14"/>
     </row>
     <row r="82" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="17"/>
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
+      <c r="A82" s="20"/>
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
       <c r="E82" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F82" s="17"/>
+        <v>59</v>
+      </c>
+      <c r="F82" s="20"/>
       <c r="G82" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H82" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H82" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I82" s="17"/>
+      <c r="I82" s="20"/>
       <c r="J82" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K82" s="9"/>
       <c r="L82" s="14"/>
     </row>
     <row r="83" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="17"/>
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
+      <c r="A83" s="20"/>
+      <c r="B83" s="20"/>
+      <c r="C83" s="20"/>
+      <c r="D83" s="20"/>
       <c r="E83" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F83" s="17"/>
+        <v>61</v>
+      </c>
+      <c r="F83" s="20"/>
       <c r="G83" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H83" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H83" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I83" s="17"/>
+      <c r="I83" s="20"/>
       <c r="J83" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K83" s="9"/>
       <c r="L83" s="14"/>
     </row>
     <row r="84" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="17"/>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
+      <c r="A84" s="20"/>
+      <c r="B84" s="20"/>
+      <c r="C84" s="20"/>
+      <c r="D84" s="20"/>
       <c r="E84" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F84" s="17"/>
+        <v>62</v>
+      </c>
+      <c r="F84" s="20"/>
       <c r="G84" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H84" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H84" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I84" s="17"/>
+      <c r="I84" s="20"/>
       <c r="J84" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K84" s="9"/>
       <c r="L84" s="14"/>
     </row>
     <row r="85" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="17"/>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
+      <c r="A85" s="20"/>
+      <c r="B85" s="20"/>
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
       <c r="E85" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F85" s="17"/>
+        <v>63</v>
+      </c>
+      <c r="F85" s="20"/>
       <c r="G85" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H85" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H85" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I85" s="17"/>
+      <c r="I85" s="20"/>
       <c r="J85" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K85" s="9"/>
       <c r="L85" s="14"/>
     </row>
     <row r="86" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="17"/>
-      <c r="B86" s="17"/>
-      <c r="C86" s="17"/>
-      <c r="D86" s="17"/>
+      <c r="A86" s="20"/>
+      <c r="B86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
       <c r="E86" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F86" s="17"/>
+        <v>64</v>
+      </c>
+      <c r="F86" s="20"/>
       <c r="G86" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H86" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H86" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I86" s="17"/>
+      <c r="I86" s="20"/>
       <c r="J86" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K86" s="9"/>
       <c r="L86" s="14"/>
     </row>
     <row r="87" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="17"/>
-      <c r="B87" s="17"/>
-      <c r="C87" s="17"/>
-      <c r="D87" s="17"/>
+      <c r="A87" s="20"/>
+      <c r="B87" s="20"/>
+      <c r="C87" s="20"/>
+      <c r="D87" s="20"/>
       <c r="E87" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F87" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="F87" s="20"/>
       <c r="G87" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H87" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="H87" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I87" s="17"/>
+      <c r="I87" s="20"/>
       <c r="J87" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K87" s="9"/>
       <c r="L87" s="14"/>
     </row>
     <row r="88" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="17"/>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17" t="s">
+      <c r="A88" s="20"/>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="D88" s="20"/>
+      <c r="E88" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" s="20"/>
+      <c r="G88" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D88" s="17"/>
-      <c r="E88" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F88" s="17"/>
-      <c r="G88" s="8" t="s">
-        <v>180</v>
-      </c>
       <c r="H88" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I88" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I88" s="20"/>
       <c r="J88" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K88" s="9"/>
       <c r="L88" s="14"/>
     </row>
     <row r="89" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="17"/>
-      <c r="B89" s="17"/>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
+      <c r="A89" s="20"/>
+      <c r="B89" s="20"/>
+      <c r="C89" s="20"/>
+      <c r="D89" s="20"/>
       <c r="E89" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="F89" s="17"/>
+        <v>59</v>
+      </c>
+      <c r="F89" s="20"/>
       <c r="G89" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I89" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I89" s="20"/>
       <c r="J89" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K89" s="9"/>
       <c r="L89" s="14"/>
     </row>
     <row r="90" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
-      <c r="C90" s="17"/>
-      <c r="D90" s="17"/>
+      <c r="A90" s="20"/>
+      <c r="B90" s="20"/>
+      <c r="C90" s="20"/>
+      <c r="D90" s="20"/>
       <c r="E90" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F90" s="17"/>
+        <v>61</v>
+      </c>
+      <c r="F90" s="20"/>
       <c r="G90" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I90" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I90" s="20"/>
       <c r="J90" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K90" s="9"/>
       <c r="L90" s="14"/>
     </row>
     <row r="91" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
-      <c r="C91" s="17"/>
-      <c r="D91" s="17"/>
+      <c r="A91" s="20"/>
+      <c r="B91" s="20"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
       <c r="E91" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F91" s="17"/>
+        <v>62</v>
+      </c>
+      <c r="F91" s="20"/>
       <c r="G91" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I91" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I91" s="20"/>
       <c r="J91" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="14"/>
     </row>
     <row r="92" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="17"/>
+      <c r="A92" s="20"/>
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
       <c r="E92" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="F92" s="17"/>
+        <v>63</v>
+      </c>
+      <c r="F92" s="20"/>
       <c r="G92" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I92" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I92" s="20"/>
       <c r="J92" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K92" s="9"/>
       <c r="L92" s="14"/>
     </row>
     <row r="93" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
-      <c r="C93" s="17"/>
-      <c r="D93" s="17"/>
+      <c r="A93" s="20"/>
+      <c r="B93" s="20"/>
+      <c r="C93" s="20"/>
+      <c r="D93" s="20"/>
       <c r="E93" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F93" s="20"/>
+      <c r="G93" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I93" s="20"/>
+      <c r="J93" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="F93" s="17"/>
-      <c r="G93" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H93" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I93" s="17"/>
-      <c r="J93" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="K93" s="9"/>
       <c r="L93" s="14"/>
     </row>
     <row r="94" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
+      <c r="A94" s="20"/>
+      <c r="B94" s="20"/>
+      <c r="C94" s="20"/>
+      <c r="D94" s="20"/>
       <c r="E94" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F94" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="F94" s="20"/>
       <c r="G94" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I94" s="17"/>
+        <v>75</v>
+      </c>
+      <c r="I94" s="20"/>
       <c r="J94" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K94" s="9"/>
       <c r="L94" s="14"/>
     </row>
     <row r="95" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="B95" s="17" t="s">
+      <c r="A95" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D95" s="17" t="s">
+      <c r="C95" s="22" t="s">
         <v>67</v>
       </c>
+      <c r="D95" s="20" t="s">
+        <v>66</v>
+      </c>
       <c r="E95" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="F95" s="17" t="s">
-        <v>137</v>
+        <v>174</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>136</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="I95" s="22" t="s">
-        <v>177</v>
+        <v>136</v>
+      </c>
+      <c r="I95" s="21" t="s">
+        <v>176</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K95" s="9"/>
       <c r="L95" s="14"/>
     </row>
     <row r="96" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
-      <c r="C96" s="21"/>
-      <c r="D96" s="17"/>
+      <c r="A96" s="20"/>
+      <c r="B96" s="20"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="20"/>
       <c r="E96" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="F96" s="20"/>
+      <c r="G96" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="I96" s="21"/>
+      <c r="J96" s="13" t="s">
         <v>176</v>
-      </c>
-      <c r="F96" s="17"/>
-      <c r="G96" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="I96" s="22"/>
-      <c r="J96" s="13" t="s">
-        <v>177</v>
       </c>
       <c r="K96" s="9"/>
       <c r="L96" s="14"/>
@@ -4144,30 +4141,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="A81:A94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="C81:C87"/>
-    <mergeCell ref="C88:C94"/>
-    <mergeCell ref="F81:F94"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A27:A80"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="C27:C53"/>
-    <mergeCell ref="C54:C80"/>
-    <mergeCell ref="B27:B80"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="B21:B26"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B81:B94"/>
     <mergeCell ref="A1:L1"/>
@@ -4184,6 +4157,30 @@
     <mergeCell ref="F7:F9"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="C12:C14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A27:A80"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="C27:C53"/>
+    <mergeCell ref="C54:C80"/>
+    <mergeCell ref="B27:B80"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="C21:C26"/>
+    <mergeCell ref="A81:A94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="C81:C87"/>
+    <mergeCell ref="C88:C94"/>
+    <mergeCell ref="F81:F94"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="F95:F96"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MeasureControl/液压测试脚本V2.xlsx
+++ b/MeasureControl/液压测试脚本V2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\application\C#\project\jiaoben\MeasureControl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\software\VisualStudio\Project\MC_jiaoben\MeasureControl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D437167E-41F5-46BB-9358-08F2B3965CB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D76DBD3-D100-4280-AAFA-EF22998F4143}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -969,6 +969,21 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -978,22 +993,7 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1298,20 +1298,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="1" customFormat="1" ht="57.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="25"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" spans="1:12" s="2" customFormat="1" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -1352,13 +1352,13 @@
       </c>
     </row>
     <row r="3" spans="1:12" s="2" customFormat="1" ht="39.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="21" t="s">
         <v>39</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -1386,9 +1386,9 @@
       <c r="L3" s="11"/>
     </row>
     <row r="4" spans="1:12" s="3" customFormat="1" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="22"/>
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="21"/>
       <c r="D4" s="8" t="s">
         <v>40</v>
       </c>
@@ -1414,10 +1414,10 @@
       <c r="L4" s="11"/>
     </row>
     <row r="5" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>44</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -1448,8 +1448,8 @@
       <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
       <c r="C6" s="15" t="s">
         <v>52</v>
       </c>
@@ -1478,22 +1478,22 @@
       <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="17" t="s">
         <v>40</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G7" s="8" t="s">
@@ -1512,14 +1512,14 @@
       <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
+      <c r="A8" s="17"/>
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
       <c r="E8" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="20"/>
+      <c r="F8" s="17"/>
       <c r="G8" s="8" t="s">
         <v>86</v>
       </c>
@@ -1536,14 +1536,14 @@
       <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
       <c r="E9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="20"/>
+      <c r="F9" s="17"/>
       <c r="G9" s="8" t="s">
         <v>86</v>
       </c>
@@ -1560,13 +1560,13 @@
       <c r="L9" s="16"/>
     </row>
     <row r="10" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -1594,9 +1594,9 @@
       <c r="L10" s="16"/>
     </row>
     <row r="11" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="8" t="s">
         <v>111</v>
       </c>
@@ -1622,13 +1622,13 @@
       <c r="L11" s="16"/>
     </row>
     <row r="12" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="17" t="s">
         <v>53</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -1656,9 +1656,9 @@
       <c r="L12" s="14"/>
     </row>
     <row r="13" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="8" t="s">
         <v>115</v>
       </c>
@@ -1684,9 +1684,9 @@
       <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="8" t="s">
         <v>114</v>
       </c>
@@ -1712,13 +1712,13 @@
       <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="17" t="s">
         <v>54</v>
       </c>
       <c r="D15" s="8" t="s">
@@ -1746,9 +1746,9 @@
       <c r="L15" s="14"/>
     </row>
     <row r="16" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="8" t="s">
         <v>117</v>
       </c>
@@ -1774,9 +1774,9 @@
       <c r="L16" s="14"/>
     </row>
     <row r="17" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="8" t="s">
         <v>121</v>
       </c>
@@ -1802,9 +1802,9 @@
       <c r="L17" s="14"/>
     </row>
     <row r="18" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="8" t="s">
         <v>120</v>
       </c>
@@ -1830,9 +1830,9 @@
       <c r="L18" s="14"/>
     </row>
     <row r="19" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="8" t="s">
         <v>119</v>
       </c>
@@ -1858,9 +1858,9 @@
       <c r="L19" s="14"/>
     </row>
     <row r="20" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
       <c r="D20" s="8" t="s">
         <v>118</v>
       </c>
@@ -1886,13 +1886,13 @@
       <c r="L20" s="14"/>
     </row>
     <row r="21" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="22" t="s">
         <v>55</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -1920,9 +1920,9 @@
       <c r="L21" s="14"/>
     </row>
     <row r="22" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="18"/>
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="8" t="s">
         <v>40</v>
       </c>
@@ -1948,9 +1948,9 @@
       <c r="L22" s="14"/>
     </row>
     <row r="23" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="8" t="s">
         <v>40</v>
       </c>
@@ -1976,9 +1976,9 @@
       <c r="L23" s="14"/>
     </row>
     <row r="24" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="8" t="s">
         <v>40</v>
       </c>
@@ -2004,9 +2004,9 @@
       <c r="L24" s="14"/>
     </row>
     <row r="25" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="8" t="s">
         <v>141</v>
       </c>
@@ -2032,9 +2032,9 @@
       <c r="L25" s="14"/>
     </row>
     <row r="26" spans="1:12" s="3" customFormat="1" ht="65.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
       <c r="D26" s="8" t="s">
         <v>142</v>
       </c>
@@ -2060,13 +2060,13 @@
       <c r="L26" s="14"/>
     </row>
     <row r="27" spans="1:12" s="3" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="17" t="s">
         <v>56</v>
       </c>
       <c r="D27" s="8" t="s">
@@ -2094,9 +2094,9 @@
       <c r="L27" s="14"/>
     </row>
     <row r="28" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
       <c r="D28" s="8" t="s">
         <v>148</v>
       </c>
@@ -2122,9 +2122,9 @@
       <c r="L28" s="14"/>
     </row>
     <row r="29" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
+      <c r="A29" s="17"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
       <c r="D29" s="8" t="s">
         <v>149</v>
       </c>
@@ -2150,9 +2150,9 @@
       <c r="L29" s="14"/>
     </row>
     <row r="30" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20"/>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
       <c r="D30" s="8" t="s">
         <v>150</v>
       </c>
@@ -2178,9 +2178,9 @@
       <c r="L30" s="14"/>
     </row>
     <row r="31" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="20"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
+      <c r="A31" s="17"/>
+      <c r="B31" s="17"/>
+      <c r="C31" s="17"/>
       <c r="D31" s="8" t="s">
         <v>151</v>
       </c>
@@ -2206,9 +2206,9 @@
       <c r="L31" s="14"/>
     </row>
     <row r="32" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="20"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
+      <c r="A32" s="17"/>
+      <c r="B32" s="17"/>
+      <c r="C32" s="17"/>
       <c r="D32" s="8" t="s">
         <v>152</v>
       </c>
@@ -2234,9 +2234,9 @@
       <c r="L32" s="14"/>
     </row>
     <row r="33" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20"/>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
+      <c r="A33" s="17"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
       <c r="D33" s="8" t="s">
         <v>153</v>
       </c>
@@ -2262,9 +2262,9 @@
       <c r="L33" s="14"/>
     </row>
     <row r="34" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="20"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="20"/>
+      <c r="A34" s="17"/>
+      <c r="B34" s="17"/>
+      <c r="C34" s="17"/>
       <c r="D34" s="8" t="s">
         <v>154</v>
       </c>
@@ -2290,9 +2290,9 @@
       <c r="L34" s="14"/>
     </row>
     <row r="35" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="20"/>
-      <c r="B35" s="20"/>
-      <c r="C35" s="20"/>
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
       <c r="D35" s="8" t="s">
         <v>155</v>
       </c>
@@ -2318,9 +2318,9 @@
       <c r="L35" s="14"/>
     </row>
     <row r="36" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="20"/>
-      <c r="B36" s="20"/>
-      <c r="C36" s="20"/>
+      <c r="A36" s="17"/>
+      <c r="B36" s="17"/>
+      <c r="C36" s="17"/>
       <c r="D36" s="8" t="s">
         <v>156</v>
       </c>
@@ -2346,9 +2346,9 @@
       <c r="L36" s="14"/>
     </row>
     <row r="37" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20"/>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
+      <c r="A37" s="17"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="17"/>
       <c r="D37" s="8" t="s">
         <v>157</v>
       </c>
@@ -2374,9 +2374,9 @@
       <c r="L37" s="14"/>
     </row>
     <row r="38" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="20"/>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
+      <c r="A38" s="17"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="17"/>
       <c r="D38" s="8" t="s">
         <v>158</v>
       </c>
@@ -2402,9 +2402,9 @@
       <c r="L38" s="14"/>
     </row>
     <row r="39" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="20"/>
-      <c r="B39" s="20"/>
-      <c r="C39" s="20"/>
+      <c r="A39" s="17"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
       <c r="D39" s="8" t="s">
         <v>159</v>
       </c>
@@ -2430,9 +2430,9 @@
       <c r="L39" s="14"/>
     </row>
     <row r="40" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="20"/>
-      <c r="B40" s="20"/>
-      <c r="C40" s="20"/>
+      <c r="A40" s="17"/>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
       <c r="D40" s="8" t="s">
         <v>160</v>
       </c>
@@ -2458,9 +2458,9 @@
       <c r="L40" s="14"/>
     </row>
     <row r="41" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="20"/>
-      <c r="B41" s="20"/>
-      <c r="C41" s="20"/>
+      <c r="A41" s="17"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
       <c r="D41" s="8" t="s">
         <v>161</v>
       </c>
@@ -2486,9 +2486,9 @@
       <c r="L41" s="14"/>
     </row>
     <row r="42" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="20"/>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
       <c r="D42" s="8" t="s">
         <v>162</v>
       </c>
@@ -2514,9 +2514,9 @@
       <c r="L42" s="14"/>
     </row>
     <row r="43" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
-      <c r="C43" s="20"/>
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
       <c r="D43" s="8" t="s">
         <v>163</v>
       </c>
@@ -2542,9 +2542,9 @@
       <c r="L43" s="14"/>
     </row>
     <row r="44" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
-      <c r="C44" s="20"/>
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="17"/>
       <c r="D44" s="8" t="s">
         <v>164</v>
       </c>
@@ -2570,9 +2570,9 @@
       <c r="L44" s="14"/>
     </row>
     <row r="45" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="20"/>
-      <c r="B45" s="20"/>
-      <c r="C45" s="20"/>
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="17"/>
       <c r="D45" s="8" t="s">
         <v>165</v>
       </c>
@@ -2598,9 +2598,9 @@
       <c r="L45" s="14"/>
     </row>
     <row r="46" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="20"/>
-      <c r="B46" s="20"/>
-      <c r="C46" s="20"/>
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="17"/>
       <c r="D46" s="8" t="s">
         <v>166</v>
       </c>
@@ -2626,9 +2626,9 @@
       <c r="L46" s="14"/>
     </row>
     <row r="47" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="20"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="20"/>
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="17"/>
       <c r="D47" s="8" t="s">
         <v>167</v>
       </c>
@@ -2654,9 +2654,9 @@
       <c r="L47" s="14"/>
     </row>
     <row r="48" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="20"/>
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
       <c r="D48" s="8" t="s">
         <v>168</v>
       </c>
@@ -2682,9 +2682,9 @@
       <c r="L48" s="14"/>
     </row>
     <row r="49" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
+      <c r="A49" s="17"/>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
       <c r="D49" s="8" t="s">
         <v>169</v>
       </c>
@@ -2710,9 +2710,9 @@
       <c r="L49" s="14"/>
     </row>
     <row r="50" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="20"/>
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
+      <c r="A50" s="17"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
       <c r="D50" s="8" t="s">
         <v>170</v>
       </c>
@@ -2738,9 +2738,9 @@
       <c r="L50" s="14"/>
     </row>
     <row r="51" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="20"/>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
+      <c r="A51" s="17"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="17"/>
       <c r="D51" s="8" t="s">
         <v>171</v>
       </c>
@@ -2766,9 +2766,9 @@
       <c r="L51" s="14"/>
     </row>
     <row r="52" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="20"/>
-      <c r="B52" s="20"/>
-      <c r="C52" s="20"/>
+      <c r="A52" s="17"/>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
       <c r="D52" s="8" t="s">
         <v>172</v>
       </c>
@@ -2794,9 +2794,9 @@
       <c r="L52" s="14"/>
     </row>
     <row r="53" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="20"/>
-      <c r="B53" s="20"/>
-      <c r="C53" s="20"/>
+      <c r="A53" s="17"/>
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
       <c r="D53" s="8" t="s">
         <v>173</v>
       </c>
@@ -2822,9 +2822,9 @@
       <c r="L53" s="14"/>
     </row>
     <row r="54" spans="1:12" s="3" customFormat="1" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="20"/>
-      <c r="B54" s="20"/>
-      <c r="C54" s="20" t="s">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17" t="s">
         <v>57</v>
       </c>
       <c r="D54" s="8" t="s">
@@ -2852,9 +2852,9 @@
       <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="20"/>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
+      <c r="A55" s="17"/>
+      <c r="B55" s="17"/>
+      <c r="C55" s="17"/>
       <c r="D55" s="8" t="s">
         <v>148</v>
       </c>
@@ -2880,9 +2880,9 @@
       <c r="L55" s="14"/>
     </row>
     <row r="56" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="20"/>
-      <c r="B56" s="20"/>
-      <c r="C56" s="20"/>
+      <c r="A56" s="17"/>
+      <c r="B56" s="17"/>
+      <c r="C56" s="17"/>
       <c r="D56" s="8" t="s">
         <v>149</v>
       </c>
@@ -2908,9 +2908,9 @@
       <c r="L56" s="14"/>
     </row>
     <row r="57" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="20"/>
-      <c r="B57" s="20"/>
-      <c r="C57" s="20"/>
+      <c r="A57" s="17"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="17"/>
       <c r="D57" s="8" t="s">
         <v>150</v>
       </c>
@@ -2936,9 +2936,9 @@
       <c r="L57" s="14"/>
     </row>
     <row r="58" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="20"/>
-      <c r="B58" s="20"/>
-      <c r="C58" s="20"/>
+      <c r="A58" s="17"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
       <c r="D58" s="8" t="s">
         <v>151</v>
       </c>
@@ -2964,9 +2964,9 @@
       <c r="L58" s="14"/>
     </row>
     <row r="59" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="20"/>
-      <c r="B59" s="20"/>
-      <c r="C59" s="20"/>
+      <c r="A59" s="17"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="17"/>
       <c r="D59" s="8" t="s">
         <v>152</v>
       </c>
@@ -2992,9 +2992,9 @@
       <c r="L59" s="14"/>
     </row>
     <row r="60" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="20"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
+      <c r="A60" s="17"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
       <c r="D60" s="8" t="s">
         <v>153</v>
       </c>
@@ -3020,9 +3020,9 @@
       <c r="L60" s="14"/>
     </row>
     <row r="61" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="17"/>
       <c r="D61" s="8" t="s">
         <v>154</v>
       </c>
@@ -3048,9 +3048,9 @@
       <c r="L61" s="14"/>
     </row>
     <row r="62" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="20"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
       <c r="D62" s="8" t="s">
         <v>155</v>
       </c>
@@ -3076,9 +3076,9 @@
       <c r="L62" s="14"/>
     </row>
     <row r="63" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="20"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="17"/>
       <c r="D63" s="8" t="s">
         <v>156</v>
       </c>
@@ -3104,9 +3104,9 @@
       <c r="L63" s="14"/>
     </row>
     <row r="64" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="20"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="17"/>
       <c r="D64" s="8" t="s">
         <v>157</v>
       </c>
@@ -3132,9 +3132,9 @@
       <c r="L64" s="14"/>
     </row>
     <row r="65" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="20"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="17"/>
       <c r="D65" s="8" t="s">
         <v>158</v>
       </c>
@@ -3160,9 +3160,9 @@
       <c r="L65" s="14"/>
     </row>
     <row r="66" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="20"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
       <c r="D66" s="8" t="s">
         <v>159</v>
       </c>
@@ -3188,9 +3188,9 @@
       <c r="L66" s="14"/>
     </row>
     <row r="67" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="20"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
       <c r="D67" s="8" t="s">
         <v>160</v>
       </c>
@@ -3216,9 +3216,9 @@
       <c r="L67" s="14"/>
     </row>
     <row r="68" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="20"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
       <c r="D68" s="8" t="s">
         <v>161</v>
       </c>
@@ -3244,9 +3244,9 @@
       <c r="L68" s="14"/>
     </row>
     <row r="69" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="20"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
       <c r="D69" s="8" t="s">
         <v>162</v>
       </c>
@@ -3272,9 +3272,9 @@
       <c r="L69" s="14"/>
     </row>
     <row r="70" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="20"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
       <c r="D70" s="8" t="s">
         <v>163</v>
       </c>
@@ -3300,9 +3300,9 @@
       <c r="L70" s="14"/>
     </row>
     <row r="71" spans="1:12" s="3" customFormat="1" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="20"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
       <c r="D71" s="8" t="s">
         <v>164</v>
       </c>
@@ -3328,9 +3328,9 @@
       <c r="L71" s="14"/>
     </row>
     <row r="72" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="20"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
       <c r="D72" s="8" t="s">
         <v>165</v>
       </c>
@@ -3356,9 +3356,9 @@
       <c r="L72" s="14"/>
     </row>
     <row r="73" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="20"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
       <c r="D73" s="8" t="s">
         <v>166</v>
       </c>
@@ -3384,9 +3384,9 @@
       <c r="L73" s="14"/>
     </row>
     <row r="74" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="20"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
       <c r="D74" s="8" t="s">
         <v>167</v>
       </c>
@@ -3412,9 +3412,9 @@
       <c r="L74" s="14"/>
     </row>
     <row r="75" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="20"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
       <c r="D75" s="8" t="s">
         <v>168</v>
       </c>
@@ -3440,9 +3440,9 @@
       <c r="L75" s="14"/>
     </row>
     <row r="76" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="20"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
+      <c r="A76" s="17"/>
+      <c r="B76" s="17"/>
+      <c r="C76" s="17"/>
       <c r="D76" s="8" t="s">
         <v>169</v>
       </c>
@@ -3468,9 +3468,9 @@
       <c r="L76" s="14"/>
     </row>
     <row r="77" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="20"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="20"/>
+      <c r="A77" s="17"/>
+      <c r="B77" s="17"/>
+      <c r="C77" s="17"/>
       <c r="D77" s="8" t="s">
         <v>170</v>
       </c>
@@ -3496,9 +3496,9 @@
       <c r="L77" s="14"/>
     </row>
     <row r="78" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="20"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
+      <c r="A78" s="17"/>
+      <c r="B78" s="17"/>
+      <c r="C78" s="17"/>
       <c r="D78" s="8" t="s">
         <v>171</v>
       </c>
@@ -3524,9 +3524,9 @@
       <c r="L78" s="14"/>
     </row>
     <row r="79" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="20"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="20"/>
+      <c r="A79" s="17"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
       <c r="D79" s="8" t="s">
         <v>172</v>
       </c>
@@ -3552,9 +3552,9 @@
       <c r="L79" s="14"/>
     </row>
     <row r="80" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="20"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="20"/>
+      <c r="A80" s="17"/>
+      <c r="B80" s="17"/>
+      <c r="C80" s="17"/>
       <c r="D80" s="8" t="s">
         <v>173</v>
       </c>
@@ -3580,22 +3580,22 @@
       <c r="L80" s="14"/>
     </row>
     <row r="81" spans="1:12" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="B81" s="20" t="s">
+      <c r="B81" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C81" s="20" t="s">
+      <c r="C81" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="D81" s="20" t="s">
+      <c r="D81" s="17" t="s">
         <v>40</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F81" s="20" t="s">
+      <c r="F81" s="17" t="s">
         <v>40</v>
       </c>
       <c r="G81" s="8" t="s">
@@ -3604,7 +3604,7 @@
       <c r="H81" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I81" s="20" t="s">
+      <c r="I81" s="17" t="s">
         <v>40</v>
       </c>
       <c r="J81" s="8" t="s">
@@ -3614,21 +3614,21 @@
       <c r="L81" s="14"/>
     </row>
     <row r="82" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="20"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
+      <c r="A82" s="17"/>
+      <c r="B82" s="17"/>
+      <c r="C82" s="17"/>
+      <c r="D82" s="17"/>
       <c r="E82" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F82" s="20"/>
+      <c r="F82" s="17"/>
       <c r="G82" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H82" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I82" s="20"/>
+      <c r="I82" s="17"/>
       <c r="J82" s="8" t="s">
         <v>180</v>
       </c>
@@ -3636,21 +3636,21 @@
       <c r="L82" s="14"/>
     </row>
     <row r="83" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="20"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
+      <c r="A83" s="17"/>
+      <c r="B83" s="17"/>
+      <c r="C83" s="17"/>
+      <c r="D83" s="17"/>
       <c r="E83" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F83" s="20"/>
+      <c r="F83" s="17"/>
       <c r="G83" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H83" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I83" s="20"/>
+      <c r="I83" s="17"/>
       <c r="J83" s="8" t="s">
         <v>180</v>
       </c>
@@ -3658,21 +3658,21 @@
       <c r="L83" s="14"/>
     </row>
     <row r="84" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="20"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
+      <c r="A84" s="17"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
       <c r="E84" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F84" s="20"/>
+      <c r="F84" s="17"/>
       <c r="G84" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H84" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I84" s="20"/>
+      <c r="I84" s="17"/>
       <c r="J84" s="8" t="s">
         <v>180</v>
       </c>
@@ -3680,21 +3680,21 @@
       <c r="L84" s="14"/>
     </row>
     <row r="85" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="20"/>
-      <c r="B85" s="20"/>
-      <c r="C85" s="20"/>
-      <c r="D85" s="20"/>
+      <c r="A85" s="17"/>
+      <c r="B85" s="17"/>
+      <c r="C85" s="17"/>
+      <c r="D85" s="17"/>
       <c r="E85" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F85" s="20"/>
+      <c r="F85" s="17"/>
       <c r="G85" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H85" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I85" s="20"/>
+      <c r="I85" s="17"/>
       <c r="J85" s="8" t="s">
         <v>180</v>
       </c>
@@ -3702,21 +3702,21 @@
       <c r="L85" s="14"/>
     </row>
     <row r="86" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="20"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
+      <c r="A86" s="17"/>
+      <c r="B86" s="17"/>
+      <c r="C86" s="17"/>
+      <c r="D86" s="17"/>
       <c r="E86" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F86" s="20"/>
+      <c r="F86" s="17"/>
       <c r="G86" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H86" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I86" s="20"/>
+      <c r="I86" s="17"/>
       <c r="J86" s="8" t="s">
         <v>180</v>
       </c>
@@ -3724,21 +3724,21 @@
       <c r="L86" s="14"/>
     </row>
     <row r="87" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="20"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="20"/>
-      <c r="D87" s="20"/>
+      <c r="A87" s="17"/>
+      <c r="B87" s="17"/>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
       <c r="E87" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F87" s="20"/>
+      <c r="F87" s="17"/>
       <c r="G87" s="8" t="s">
         <v>74</v>
       </c>
       <c r="H87" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I87" s="20"/>
+      <c r="I87" s="17"/>
       <c r="J87" s="8" t="s">
         <v>180</v>
       </c>
@@ -3746,23 +3746,23 @@
       <c r="L87" s="14"/>
     </row>
     <row r="88" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="20"/>
-      <c r="B88" s="20"/>
-      <c r="C88" s="20" t="s">
+      <c r="A88" s="17"/>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D88" s="20"/>
+      <c r="D88" s="17"/>
       <c r="E88" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F88" s="20"/>
+      <c r="F88" s="17"/>
       <c r="G88" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H88" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I88" s="20"/>
+      <c r="I88" s="17"/>
       <c r="J88" s="8" t="s">
         <v>65</v>
       </c>
@@ -3770,21 +3770,21 @@
       <c r="L88" s="14"/>
     </row>
     <row r="89" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="20"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="20"/>
-      <c r="D89" s="20"/>
+      <c r="A89" s="17"/>
+      <c r="B89" s="17"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
       <c r="E89" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F89" s="20"/>
+      <c r="F89" s="17"/>
       <c r="G89" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H89" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I89" s="20"/>
+      <c r="I89" s="17"/>
       <c r="J89" s="8" t="s">
         <v>65</v>
       </c>
@@ -3792,21 +3792,21 @@
       <c r="L89" s="14"/>
     </row>
     <row r="90" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="20"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="20"/>
-      <c r="D90" s="20"/>
+      <c r="A90" s="17"/>
+      <c r="B90" s="17"/>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
       <c r="E90" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F90" s="20"/>
+      <c r="F90" s="17"/>
       <c r="G90" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H90" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I90" s="20"/>
+      <c r="I90" s="17"/>
       <c r="J90" s="8" t="s">
         <v>65</v>
       </c>
@@ -3814,21 +3814,21 @@
       <c r="L90" s="14"/>
     </row>
     <row r="91" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="20"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
+      <c r="A91" s="17"/>
+      <c r="B91" s="17"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
       <c r="E91" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F91" s="20"/>
+      <c r="F91" s="17"/>
       <c r="G91" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H91" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I91" s="20"/>
+      <c r="I91" s="17"/>
       <c r="J91" s="8" t="s">
         <v>65</v>
       </c>
@@ -3836,21 +3836,21 @@
       <c r="L91" s="14"/>
     </row>
     <row r="92" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="20"/>
-      <c r="B92" s="20"/>
-      <c r="C92" s="20"/>
-      <c r="D92" s="20"/>
+      <c r="A92" s="17"/>
+      <c r="B92" s="17"/>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
       <c r="E92" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F92" s="20"/>
+      <c r="F92" s="17"/>
       <c r="G92" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H92" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I92" s="20"/>
+      <c r="I92" s="17"/>
       <c r="J92" s="8" t="s">
         <v>65</v>
       </c>
@@ -3858,21 +3858,21 @@
       <c r="L92" s="14"/>
     </row>
     <row r="93" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="20"/>
-      <c r="B93" s="20"/>
-      <c r="C93" s="20"/>
-      <c r="D93" s="20"/>
+      <c r="A93" s="17"/>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
       <c r="E93" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F93" s="20"/>
+      <c r="F93" s="17"/>
       <c r="G93" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H93" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I93" s="20"/>
+      <c r="I93" s="17"/>
       <c r="J93" s="8" t="s">
         <v>65</v>
       </c>
@@ -3880,21 +3880,21 @@
       <c r="L93" s="14"/>
     </row>
     <row r="94" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="20"/>
-      <c r="B94" s="20"/>
-      <c r="C94" s="20"/>
-      <c r="D94" s="20"/>
+      <c r="A94" s="17"/>
+      <c r="B94" s="17"/>
+      <c r="C94" s="17"/>
+      <c r="D94" s="17"/>
       <c r="E94" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="F94" s="20"/>
+      <c r="F94" s="17"/>
       <c r="G94" s="8" t="s">
         <v>179</v>
       </c>
       <c r="H94" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="I94" s="20"/>
+      <c r="I94" s="17"/>
       <c r="J94" s="8" t="s">
         <v>65</v>
       </c>
@@ -3902,22 +3902,22 @@
       <c r="L94" s="14"/>
     </row>
     <row r="95" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="20" t="s">
+      <c r="A95" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B95" s="20" t="s">
+      <c r="B95" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C95" s="22" t="s">
+      <c r="C95" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="D95" s="20" t="s">
+      <c r="D95" s="17" t="s">
         <v>66</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="F95" s="20" t="s">
+      <c r="F95" s="17" t="s">
         <v>136</v>
       </c>
       <c r="G95" s="8" t="s">
@@ -3926,7 +3926,7 @@
       <c r="H95" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I95" s="21" t="s">
+      <c r="I95" s="25" t="s">
         <v>176</v>
       </c>
       <c r="J95" s="13" t="s">
@@ -3936,21 +3936,21 @@
       <c r="L95" s="14"/>
     </row>
     <row r="96" spans="1:12" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="20"/>
-      <c r="B96" s="20"/>
-      <c r="C96" s="22"/>
-      <c r="D96" s="20"/>
+      <c r="A96" s="17"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="21"/>
+      <c r="D96" s="17"/>
       <c r="E96" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F96" s="20"/>
+      <c r="F96" s="17"/>
       <c r="G96" s="8" t="s">
         <v>80</v>
       </c>
       <c r="H96" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I96" s="21"/>
+      <c r="I96" s="25"/>
       <c r="J96" s="13" t="s">
         <v>176</v>
       </c>
@@ -4141,6 +4141,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A81:A94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="C81:C87"/>
+    <mergeCell ref="C88:C94"/>
+    <mergeCell ref="F81:F94"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="A27:A80"/>
+    <mergeCell ref="B15:B20"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="C15:C20"/>
+    <mergeCell ref="C27:C53"/>
+    <mergeCell ref="C54:C80"/>
+    <mergeCell ref="B27:B80"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="B21:B26"/>
+    <mergeCell ref="C21:C26"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="B81:B94"/>
     <mergeCell ref="A1:L1"/>
@@ -4157,30 +4181,6 @@
     <mergeCell ref="F7:F9"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="C12:C14"/>
-    <mergeCell ref="B12:B14"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="A27:A80"/>
-    <mergeCell ref="B15:B20"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="C15:C20"/>
-    <mergeCell ref="C27:C53"/>
-    <mergeCell ref="C54:C80"/>
-    <mergeCell ref="B27:B80"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="B21:B26"/>
-    <mergeCell ref="C21:C26"/>
-    <mergeCell ref="A81:A94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="C81:C87"/>
-    <mergeCell ref="C88:C94"/>
-    <mergeCell ref="F81:F94"/>
-    <mergeCell ref="B95:B96"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="F95:F96"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
